--- a/0_1_Output_Data/5_ifo_qoq_error_series_GVA_matched_to_ifoCAST/ifo_qoq_matched_errors_latest_GVA.xlsx
+++ b/0_1_Output_Data/5_ifo_qoq_error_series_GVA_matched_to_ifoCAST/ifo_qoq_matched_errors_latest_GVA.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>Q0</t>
   </si>
@@ -113,6 +113,9 @@
   </si>
   <si>
     <t>2025-08-22 00:00:00_diff</t>
+  </si>
+  <si>
+    <t>2025-11-25 00:00:00_diff</t>
   </si>
 </sst>
 </file>
@@ -470,7 +473,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -1106,6 +1109,11 @@
         <v>0.02940328597706714</v>
       </c>
     </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
